--- a/output/pdf_financials_xlsx/RAD.xlsx
+++ b/output/pdf_financials_xlsx/RAD.xlsx
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.407916</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.295233</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.178108</v>
       </c>
     </row>
     <row r="35">
@@ -1180,13 +1180,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.407916</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.295233</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.178108</v>
       </c>
     </row>
     <row r="37">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.415266</v>
+        <v>0.00735</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.302733</v>
+        <v>0.0075</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.185608</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="49">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
